--- a/data/trans_orig/IP07A09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A09-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11161</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>27573</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45231</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>33831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49837</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29956</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47389</t>
+          <t>48193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68618</t>
+          <t>68504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92897</t>
+          <t>92744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>54312</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>70842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69401</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89031</t>
+          <t>89305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130131</t>
+          <t>128865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156634</t>
+          <t>155828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>30167</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49026</t>
+          <t>48171</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>32124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49304</t>
+          <t>50293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67822</t>
+          <t>67295</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93300</t>
+          <t>92975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>34881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54452</t>
+          <t>52870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>45208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66749</t>
+          <t>66142</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85987</t>
+          <t>86178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114322</t>
+          <t>113120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93063</t>
+          <t>94382</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115462</t>
+          <t>115946</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93805</t>
+          <t>92877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115648</t>
+          <t>117001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192660</t>
+          <t>192088</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224102</t>
+          <t>226818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>66725</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>48563</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69518</t>
+          <t>71517</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99594</t>
+          <t>99149</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>130611</t>
+          <t>132525</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74085</t>
+          <t>74072</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100227</t>
+          <t>100925</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81055</t>
+          <t>80532</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107756</t>
+          <t>107787</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>161759</t>
+          <t>159308</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198500</t>
+          <t>197985</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153085</t>
+          <t>152642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182132</t>
+          <t>181542</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>168651</t>
+          <t>169518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>199313</t>
+          <t>199292</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>332172</t>
+          <t>332759</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>374275</t>
+          <t>373044</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>17432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32952</t>
+          <t>32521</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>24686</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41369</t>
+          <t>42050</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46212</t>
+          <t>46111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68884</t>
+          <t>69256</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23583</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39412</t>
+          <t>38284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39699</t>
+          <t>39055</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50911</t>
+          <t>50481</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74395</t>
+          <t>72450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82045</t>
+          <t>81763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101437</t>
+          <t>101130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74494</t>
+          <t>74825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95358</t>
+          <t>95243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161237</t>
+          <t>160593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190209</t>
+          <t>190699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>17179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>29562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47847</t>
+          <t>46998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28490</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46057</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62201</t>
+          <t>62426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87745</t>
+          <t>87960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>39912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59617</t>
+          <t>59193</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>29194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47059</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74015</t>
+          <t>73284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100888</t>
+          <t>100408</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57057</t>
+          <t>58111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79130</t>
+          <t>78664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83666</t>
+          <t>85420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105154</t>
+          <t>105837</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147247</t>
+          <t>145830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176763</t>
+          <t>176984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>16089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>51275</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74907</t>
+          <t>75917</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57180</t>
+          <t>57721</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81200</t>
+          <t>81667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114564</t>
+          <t>115080</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>148332</t>
+          <t>149661</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67463</t>
+          <t>67223</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92260</t>
+          <t>92671</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56556</t>
+          <t>56303</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81069</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>132123</t>
+          <t>132114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166518</t>
+          <t>168183</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>144735</t>
+          <t>144453</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173962</t>
+          <t>173556</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>165431</t>
+          <t>164193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>194380</t>
+          <t>195152</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>316022</t>
+          <t>316210</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>358680</t>
+          <t>358429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36984</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28051</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45785</t>
+          <t>45986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52815</t>
+          <t>52801</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76473</t>
+          <t>77245</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42802</t>
+          <t>41683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>62065</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34117</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>53798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80999</t>
+          <t>82490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109752</t>
+          <t>110492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83653</t>
+          <t>83388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105332</t>
+          <t>105937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85830</t>
+          <t>85586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108103</t>
+          <t>108339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173874</t>
+          <t>175804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>207989</t>
+          <t>206635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14111</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>19568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>28902</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47444</t>
+          <t>46782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28233</t>
+          <t>28072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45673</t>
+          <t>45791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61214</t>
+          <t>62129</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>86251</t>
+          <t>86149</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38772</t>
+          <t>39215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58910</t>
+          <t>59081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>41716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63341</t>
+          <t>62261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87434</t>
+          <t>86952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115011</t>
+          <t>114940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60758</t>
+          <t>60537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83052</t>
+          <t>82601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67074</t>
+          <t>66426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88337</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135711</t>
+          <t>135833</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166215</t>
+          <t>166070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>34297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>78490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>59969</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86051</t>
+          <t>84510</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120513</t>
+          <t>121787</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156118</t>
+          <t>156642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87837</t>
+          <t>87630</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116149</t>
+          <t>115993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>82815</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109629</t>
+          <t>109701</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>175493</t>
+          <t>176758</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>215735</t>
+          <t>217771</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150878</t>
+          <t>150191</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183520</t>
+          <t>183003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159580</t>
+          <t>159487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>191269</t>
+          <t>192044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>320986</t>
+          <t>319149</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366775</t>
+          <t>363224</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A09-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2230</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5960</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5328</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -840,67 +840,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>2747</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6516</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6905</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18653</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12946</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26265</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18,56%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>16620</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11355</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23540</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10993</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>23682</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,16%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,65%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18653</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12639</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26044</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27573</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>45071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38136</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29718</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>46571</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>41532</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33831</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>50406</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>33319</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>50472</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>32,9%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>38136</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>30440</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>48193</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>26,95%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68504</t>
+          <t>68354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92744</t>
+          <t>92233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80022</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>70366</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>89522</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>56,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>63123</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>54312</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>70842</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>54084</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72224</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>50,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>43,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>56,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>80022</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>70628</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>89305</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>56,55%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128865</t>
+          <t>129239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155828</t>
+          <t>156051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126252</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126252</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126252</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1943</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5321</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1257</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4353</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4520</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1666</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9627</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9441</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2134</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5067</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39922</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31058</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>50045</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>15,22%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24,52%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>39135</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30167</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48171</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>31026</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>48577</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>20,16%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39922</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32124</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>50293</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67295</t>
+          <t>66880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92975</t>
+          <t>93615</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>55417</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45140</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65539</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>43989</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34881</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52870</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34642</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54482</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,66%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>55417</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>45208</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>66142</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,16%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86178</t>
+          <t>86308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113120</t>
+          <t>114292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105342</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>94578</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116649</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>104510</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>94382</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>115946</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>93105</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>115144</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,84%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>48,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105342</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>92877</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>117001</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192088</t>
+          <t>194025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226818</t>
+          <t>225814</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,71%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7360</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4173</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1493</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8952</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8167</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3222</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1241</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7595</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4873</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10098</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>7267</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3815</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12885</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12558</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>4873</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>9226</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>58575</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>48311</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>70486</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>16,95%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13,98%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>55755</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>45696</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>66725</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>44960</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>67211</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>17,4%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,26%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>58575</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>48563</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99149</t>
+          <t>99292</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>132525</t>
+          <t>131004</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>93553</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>80819</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>107765</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>23,39%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>85521</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>74072</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>100925</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>73070</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>98323</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>26,7%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>23,12%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>31,5%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>93553</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>80532</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>107787</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>27,07%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>159308</t>
+          <t>160950</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197985</t>
+          <t>199835</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>185363</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>171301</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>200263</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>53,64%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>49,57%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>57,95%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>167632</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>152642</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>181542</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>152147</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>182772</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>52,33%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>47,65%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>56,67%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>185363</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>169518</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>199292</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>53,64%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>332759</t>
+          <t>330159</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>373044</t>
+          <t>375089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>320349</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>320349</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>320349</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3426</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7764</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5669</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2875</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10587</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2653</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10447</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3426</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5473</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2471</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10043</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2737</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6531</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6630</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5473</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2629</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10231</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13304</t>
+          <t>13963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32528</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23733</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41276</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>26,34%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24385</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17432</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32521</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17888</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>33663</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>15,75%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,26%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>32528</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24686</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42050</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46111</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69256</t>
+          <t>69208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30623</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22710</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39079</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>30548</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22362</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38284</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>23070</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>38766</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>30623</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23488</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>39055</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50481</t>
+          <t>51135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72450</t>
+          <t>73506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84624</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75074</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>94793</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>60,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>91457</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>81763</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>101130</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80566</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100580</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>59,08%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>84624</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>74825</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>95243</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>54,01%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160593</t>
+          <t>160741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190699</t>
+          <t>190659</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>154796</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>154796</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>154796</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4973</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5609</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2570</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11033</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10887</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4539</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4581</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1877</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8885</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6530</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3258</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11796</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3072</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12011</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4581</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9103</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36342</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28222</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45704</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>20,82%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16,17%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26,18%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>38221</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29562</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>46998</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>29353</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>47393</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>22,87%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28,12%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>36342</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27556</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>44625</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62426</t>
+          <t>62965</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87960</t>
+          <t>87983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37476</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29398</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46043</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>49586</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39912</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>59193</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41099</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>60085</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>29,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>37476</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>29194</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>46595</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,47%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73284</t>
+          <t>74048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100408</t>
+          <t>101035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>94826</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>85017</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>106511</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>61,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>67184</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>58111</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>78664</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>56639</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>77592</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>40,2%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>47,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>94826</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>85420</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>105837</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>54,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145830</t>
+          <t>146804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176984</t>
+          <t>175961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174562</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174562</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174562</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174562</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174562</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174562</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4764</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>11278</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6520</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18008</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6845</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17279</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4764</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9161</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>23921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10054</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5584</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15933</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>9267</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5349</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16089</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5125</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15295</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2,88%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>10054</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>5740</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>15871</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27010</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>68871</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>57763</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>81450</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>24,59%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>62606</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>51275</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>75917</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>51638</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>75784</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>19,45%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>68871</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>57721</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>81667</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>20,79%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115080</t>
+          <t>115426</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149661</t>
+          <t>150409</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>68099</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>57558</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>80902</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20,56%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>17,38%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,42%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>80134</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>67223</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>92671</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>67247</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>93109</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>24,89%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>28,79%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>68099</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>56303</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>80081</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>132114</t>
+          <t>131033</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>168183</t>
+          <t>165945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>179450</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>164956</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>193742</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>54,18%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>58,49%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>158641</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>144453</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>173556</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>143411</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>173382</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>49,28%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>44,87%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>53,91%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>179450</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>164193</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>195152</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>54,18%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>316210</t>
+          <t>316114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>358429</t>
+          <t>358174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>331237</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>331237</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>331237</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321926</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321926</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321926</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>331237</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>331237</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>331237</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4808</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10154</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3768</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1738</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8563</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7757</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4808</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9613</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6437</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2915</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11047</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6447</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2991</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11273</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3520</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12272</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>3,48%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6437</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3015</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11593</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35966</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>27384</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>45873</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>19,2%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>24,49%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>28284</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>21042</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>37420</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>20985</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>37032</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>15,25%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>35966</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>27733</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>45986</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>19,2%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52801</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77245</t>
+          <t>77356</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43249</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34222</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53720</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>51996</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>41683</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>42311</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>62883</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>28,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>43249</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>33783</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>53798</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>23,09%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82490</t>
+          <t>80804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110492</t>
+          <t>109374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96854</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83977</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>107043</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>57,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>94924</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>83388</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>105937</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>83452</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>106970</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>51,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,97%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>57,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96854</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>85586</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108339</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>51,71%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175804</t>
+          <t>175624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206635</t>
+          <t>207763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185419</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185419</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185419</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5961,67 +5961,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>4035</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9392</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>3873</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8488</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8793</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4035</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9046</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3027</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6995</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>9030</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4936</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16581</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4751</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15121</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>5,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3027</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7106</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19568</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36401</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28247</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46402</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>20,91%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26,66%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37064</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>28902</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>46782</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>29188</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>45768</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>21,7%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>27,39%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>36401</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28072</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>45791</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>20,91%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62129</t>
+          <t>61227</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>86149</t>
+          <t>86167</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52051</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42852</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>63397</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>48998</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39215</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>59081</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>39618</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>59507</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>28,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>52051</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>41716</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62261</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>29,91%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86952</t>
+          <t>87080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114940</t>
+          <t>116475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78533</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67896</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>90058</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>39,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>71825</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>60537</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>82601</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>60353</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>82924</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>42,05%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>48,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78533</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>66426</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>90094</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>45,12%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135833</t>
+          <t>136947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166070</t>
+          <t>166163</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8843</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4858</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14529</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>7641</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13223</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4061</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13453</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8843</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4782</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14775</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9465</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15979</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>15477</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>10089</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22865</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>9394</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>23125</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>4,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>9465</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>5117</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>15181</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34297</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>72367</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>59766</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>85570</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>65348</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>55157</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>78490</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>54171</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>79265</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>18,35%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>72367</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>59969</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>84510</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121787</t>
+          <t>121814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156642</t>
+          <t>157289</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>95300</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>82637</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>110161</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>26,37%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>22,87%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>30,48%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>100993</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>87630</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>115993</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>87742</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>115276</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>28,35%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>24,6%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>32,56%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>95300</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>82815</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>109701</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>26,37%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>176758</t>
+          <t>176868</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>217771</t>
+          <t>217431</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>175387</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>159534</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>190426</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>48,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>44,15%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>166749</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>150191</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>183003</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>151423</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>183051</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>46,81%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>42,16%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>51,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>159487</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>192044</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>48,54%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319149</t>
+          <t>319012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>363224</t>
+          <t>363399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>356208</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>356208</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>356208</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
